--- a/Gantt-chart TIMELINE per 12 Maret 2026.xlsx
+++ b/Gantt-chart TIMELINE per 12 Maret 2026.xlsx
@@ -853,7 +853,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="249">
   <si>
     <t xml:space="preserve">Project Start Date </t>
   </si>
@@ -1024,12 +1024,6 @@
   </si>
   <si>
     <t>Buat UI penarikan data dari API dan insert data Reservasi</t>
-  </si>
-  <si>
-    <t>REPORT CANCEL KAIN KELUAR</t>
-  </si>
-  <si>
-    <t>REPORT CANCEL KAIN MASUK</t>
   </si>
   <si>
     <t>REPORT COSTING ?</t>
@@ -2306,9 +2300,6 @@
     <t>https://www.vertex42.com/licensing/EULA_privateuse.html</t>
   </si>
   <si>
-    <t>Form Outbound Delivery sudah dilengkapi</t>
-  </si>
-  <si>
     <t>Modifikasi Form Transfer Posting</t>
   </si>
   <si>
@@ -2327,18 +2318,6 @@
     <t>Libur lebaran 18-26 February</t>
   </si>
   <si>
-    <t>Stock Per Barcode sudah selesai</t>
-  </si>
-  <si>
-    <t>Stock Leadtime sudah selesai</t>
-  </si>
-  <si>
-    <t>List Karton per kode order sudah selesai</t>
-  </si>
-  <si>
-    <t>Packing Lead Time sudah selesai</t>
-  </si>
-  <si>
     <t>Moving History Per List Barcode</t>
   </si>
   <si>
@@ -2361,6 +2340,21 @@
   </si>
   <si>
     <t>Update per 12 Maret 2026</t>
+  </si>
+  <si>
+    <t>CANCEL</t>
+  </si>
+  <si>
+    <t>REPORT CANCEL KAIN KELUAR tidak perlu dibuat karena tidak ada cancel di SAP</t>
+  </si>
+  <si>
+    <t>REPORT CANCEL KAIN MASUK  tidak perlu dibuat karena tidak ada cancel di SAP</t>
+  </si>
+  <si>
+    <t>REPORT CANCEL KAIN KELUAR(TIDAK DIBUAT)</t>
+  </si>
+  <si>
+    <t>REPORT CANCEL KAIN MASUK(TIDAK DIBUAT)</t>
   </si>
 </sst>
 </file>
@@ -2689,7 +2683,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2771,6 +2765,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor rgb="FFD6F4D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor rgb="FFD6F4D9"/>
       </patternFill>
     </fill>
@@ -2963,7 +2969,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3316,6 +3322,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="15" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3827,13 +3860,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3869,13 +3902,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4217,7 +4250,7 @@
   <sheetData>
     <row r="1" spans="1:66" ht="30" customHeight="1">
       <c r="A1" s="56" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -8283,30 +8316,30 @@
       <c r="BN45" s="4"/>
     </row>
     <row r="46" spans="1:66" s="1" customFormat="1" ht="18">
-      <c r="A46" s="4" t="str">
+      <c r="A46" s="126" t="str">
         <f t="shared" si="14"/>
         <v>1.38</v>
       </c>
-      <c r="B46" s="93" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="B46" s="127" t="s">
+        <v>247</v>
+      </c>
+      <c r="C46" s="128" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="6">
+      <c r="D46" s="129"/>
+      <c r="E46" s="130">
         <f>F43+1</f>
         <v>46087</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="131">
         <f t="shared" si="33"/>
         <v>46090</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="132">
         <v>4</v>
       </c>
-      <c r="H46" s="9">
-        <v>0</v>
+      <c r="H46" s="133" t="s">
+        <v>244</v>
       </c>
       <c r="I46" s="10">
         <f t="shared" si="34"/>
@@ -8371,30 +8404,30 @@
       <c r="BN46" s="4"/>
     </row>
     <row r="47" spans="1:66" s="1" customFormat="1" ht="18">
-      <c r="A47" s="4" t="str">
+      <c r="A47" s="126" t="str">
         <f t="shared" si="14"/>
         <v>1.39</v>
       </c>
-      <c r="B47" s="93" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="B47" s="127" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="6">
+      <c r="D47" s="129"/>
+      <c r="E47" s="130">
         <f>F44+1</f>
         <v>46087</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="131">
         <f t="shared" si="33"/>
         <v>46090</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="132">
         <v>4</v>
       </c>
-      <c r="H47" s="9">
-        <v>0</v>
+      <c r="H47" s="133" t="s">
+        <v>244</v>
       </c>
       <c r="I47" s="10">
         <f t="shared" si="34"/>
@@ -8464,14 +8497,14 @@
         <v>1.40</v>
       </c>
       <c r="B48" s="99" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="6">
-        <f t="shared" ref="E48:E53" si="37">F46+1</f>
+        <f>F46+1</f>
         <v>46091</v>
       </c>
       <c r="F48" s="7">
@@ -8552,14 +8585,14 @@
         <v>1.41</v>
       </c>
       <c r="B49" s="93" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="6">
-        <f t="shared" si="37"/>
+        <f>F47+1</f>
         <v>46091</v>
       </c>
       <c r="F49" s="7">
@@ -8640,14 +8673,14 @@
         <v>1.42</v>
       </c>
       <c r="B50" s="93" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="E50:E53" si="37">F48+1</f>
         <v>46093</v>
       </c>
       <c r="F50" s="7">
@@ -8728,7 +8761,7 @@
         <v>1.43</v>
       </c>
       <c r="B51" s="93" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>51</v>
@@ -8816,7 +8849,7 @@
         <v>1.44</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>28</v>
@@ -8904,7 +8937,7 @@
         <v>1.45</v>
       </c>
       <c r="B53" s="98" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>51</v>
@@ -8992,7 +9025,7 @@
         <v>1.46</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>28</v>
@@ -9080,7 +9113,7 @@
         <v>1.47</v>
       </c>
       <c r="B55" s="98" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>51</v>
@@ -9168,7 +9201,7 @@
         <v>1.48</v>
       </c>
       <c r="B56" s="98" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>28</v>
@@ -9256,7 +9289,7 @@
         <v>1.49</v>
       </c>
       <c r="B57" s="93" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>51</v>
@@ -9344,7 +9377,7 @@
         <v>1.50</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>51</v>
@@ -9432,7 +9465,7 @@
         <v>1.51</v>
       </c>
       <c r="B59" s="94" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C59" s="95" t="s">
         <v>54</v>
@@ -9520,7 +9553,7 @@
         <v>1.52</v>
       </c>
       <c r="B60" s="93" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>28</v>
@@ -10546,19 +10579,19 @@
         <v>1</v>
       </c>
       <c r="B76" s="101" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D76" s="102"/>
       <c r="E76" s="103"/>
       <c r="F76" s="103" t="str">
         <f t="shared" ref="F76:F81" si="38">IF(ISBLANK(E76)," - ",IF(G76=0,E76,E76+G76-1))</f>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="G76" s="104"/>
       <c r="H76" s="105"/>
       <c r="I76" s="106" t="str">
         <f t="shared" ref="I76:I81" si="39">IF(OR(F76=0,E76=0)," - ",NETWORKDAYS(E76,F76))</f>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="J76" s="107"/>
       <c r="K76" s="108"/>
@@ -10624,10 +10657,10 @@
         <v>1.1</v>
       </c>
       <c r="B77" s="93" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="6">
@@ -10711,7 +10744,7 @@
         <v>1.2</v>
       </c>
       <c r="B78" s="93" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>19</v>
@@ -10798,7 +10831,7 @@
         <v>1.3</v>
       </c>
       <c r="B79" s="93" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>28</v>
@@ -10885,7 +10918,7 @@
         <v>1.4</v>
       </c>
       <c r="B80" s="93" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>19</v>
@@ -10972,7 +11005,7 @@
         <v>1.5</v>
       </c>
       <c r="B81" s="93" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>28</v>
@@ -11059,7 +11092,7 @@
         <v>1.6</v>
       </c>
       <c r="B82" s="93" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>19</v>
@@ -11146,7 +11179,7 @@
         <v>1.7</v>
       </c>
       <c r="B83" s="93" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>28</v>
@@ -11233,10 +11266,10 @@
         <v>1.8</v>
       </c>
       <c r="B84" s="93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="6">
@@ -11320,7 +11353,7 @@
         <v>1.9</v>
       </c>
       <c r="B85" s="93" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>19</v>
@@ -11407,7 +11440,7 @@
         <v>1.10</v>
       </c>
       <c r="B86" s="93" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>28</v>
@@ -11494,7 +11527,7 @@
         <v>1.11</v>
       </c>
       <c r="B87" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>28</v>
@@ -11581,7 +11614,7 @@
         <v>1.12</v>
       </c>
       <c r="B88" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>19</v>
@@ -11668,7 +11701,7 @@
         <v>1.13</v>
       </c>
       <c r="B89" s="93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>28</v>
@@ -11755,7 +11788,7 @@
         <v>1.14</v>
       </c>
       <c r="B90" s="93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>28</v>
@@ -11842,7 +11875,7 @@
         <v>1.15</v>
       </c>
       <c r="B91" s="93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>28</v>
@@ -11929,7 +11962,7 @@
         <v>1.16</v>
       </c>
       <c r="B92" s="93" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>28</v>
@@ -12016,7 +12049,7 @@
         <v>1.17</v>
       </c>
       <c r="B93" s="93" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>19</v>
@@ -12103,7 +12136,7 @@
         <v>1.18</v>
       </c>
       <c r="B94" s="93" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>28</v>
@@ -12190,7 +12223,7 @@
         <v>1.19</v>
       </c>
       <c r="B95" s="93" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>19</v>
@@ -12277,7 +12310,7 @@
         <v>1.20</v>
       </c>
       <c r="B96" s="93" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>28</v>
@@ -12364,7 +12397,7 @@
         <v>1.21</v>
       </c>
       <c r="B97" s="93" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>19</v>
@@ -12451,7 +12484,7 @@
         <v>1.22</v>
       </c>
       <c r="B98" s="93" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>28</v>
@@ -12538,7 +12571,7 @@
         <v>1.23</v>
       </c>
       <c r="B99" s="93" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>19</v>
@@ -12625,7 +12658,7 @@
         <v>1.24</v>
       </c>
       <c r="B100" s="93" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>28</v>
@@ -12712,7 +12745,7 @@
         <v>1.25</v>
       </c>
       <c r="B101" s="93" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>28</v>
@@ -12799,7 +12832,7 @@
         <v>1.26</v>
       </c>
       <c r="B102" s="93" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>28</v>
@@ -12886,7 +12919,7 @@
         <v>1.27</v>
       </c>
       <c r="B103" s="93" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>28</v>
@@ -12973,19 +13006,19 @@
         <v>2</v>
       </c>
       <c r="B104" s="101" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D104" s="102"/>
       <c r="E104" s="103"/>
       <c r="F104" s="103" t="str">
         <f t="shared" si="47"/>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="G104" s="104"/>
       <c r="H104" s="105"/>
       <c r="I104" s="106" t="str">
         <f t="shared" si="48"/>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="J104" s="107"/>
       <c r="K104" s="108"/>
@@ -13051,10 +13084,10 @@
         <v>2.1</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="6">
@@ -13138,10 +13171,10 @@
         <v>2.2</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="6">
@@ -13224,10 +13257,10 @@
         <v>2.3</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="6">
@@ -13310,19 +13343,19 @@
         <v>3</v>
       </c>
       <c r="B108" s="101" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D108" s="102"/>
       <c r="E108" s="103"/>
       <c r="F108" s="103" t="str">
         <f t="shared" ref="F108:F113" si="53">IF(ISBLANK(E108)," - ",IF(G108=0,E108,E108+G108-1))</f>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="G108" s="104"/>
       <c r="H108" s="105"/>
       <c r="I108" s="106" t="str">
         <f t="shared" ref="I108" si="54">IF(OR(F108=0,E108=0)," - ",NETWORKDAYS(E108,F108))</f>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="J108" s="107"/>
       <c r="K108" s="108"/>
@@ -13388,10 +13421,10 @@
         <v>3.1</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="6">
@@ -13474,10 +13507,10 @@
         <v>3.2</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="6">
@@ -13560,7 +13593,7 @@
         <v>3.3</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>19</v>
@@ -13646,7 +13679,7 @@
         <v>3.4</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>19</v>
@@ -13732,7 +13765,7 @@
         <v>3.5</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>28</v>
@@ -13818,19 +13851,19 @@
         <v>4</v>
       </c>
       <c r="B114" s="101" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D114" s="102"/>
       <c r="E114" s="103"/>
       <c r="F114" s="103" t="str">
         <f t="shared" ref="F114:F115" si="55">IF(ISBLANK(E114)," - ",IF(G114=0,E114,E114+G114-1))</f>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="G114" s="104"/>
       <c r="H114" s="105"/>
       <c r="I114" s="106" t="str">
         <f t="shared" ref="I114" si="56">IF(OR(F114=0,E114=0)," - ",NETWORKDAYS(E114,F114))</f>
-        <v>-</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="J114" s="107"/>
       <c r="K114" s="108"/>
@@ -13896,10 +13929,10 @@
         <v>4.1</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="6">
@@ -14499,21 +14532,21 @@
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Enter the week number to display first in the Gantt Chart. The weeks are numbered starting from the week containing the Project Start Date." sqref="H4"/>
   </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.25"/>
-  <pageSetup scale="53" orientation="landscape"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="36" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
     <ignoredError sqref="A76" formula="1"/>
     <ignoredError sqref="H78:H80 G76:H76 E76" unlockedFormula="1"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8238" r:id="rId3" name="Scroll Bar 46">
+            <control shapeId="8238" r:id="rId4" name="Scroll Bar 46">
               <controlPr defaultSize="0" print="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15056,162 +15089,162 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="C4" s="36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18">
       <c r="C7" s="52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="C8" s="53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18">
       <c r="C13" s="52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75">
       <c r="A16" s="27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15">
       <c r="B18" s="54" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15">
       <c r="B22" s="54" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="15">
       <c r="B26" s="54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="15">
       <c r="B34" s="54" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="15">
       <c r="B39" s="54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="15">
       <c r="B42" s="54" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="18">
       <c r="B46" s="52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -15239,13 +15272,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="14.25">
       <c r="A2" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B2" s="25"/>
     </row>
@@ -15254,88 +15287,88 @@
     </row>
     <row r="4" spans="1:3" ht="18">
       <c r="A4" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B4" s="27"/>
     </row>
     <row r="5" spans="1:3" ht="57">
       <c r="B5" s="28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.5">
       <c r="B7" s="28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25">
       <c r="B9" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.5">
       <c r="B11" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18">
       <c r="A13" s="124" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B13" s="124"/>
     </row>
     <row r="15" spans="1:3" s="22" customFormat="1" ht="18">
       <c r="A15" s="30"/>
       <c r="B15" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="22" customFormat="1" ht="18">
       <c r="A16" s="30"/>
       <c r="B16" s="31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18">
       <c r="A17" s="33"/>
       <c r="B17" s="31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18">
       <c r="A18" s="33"/>
       <c r="B18" s="31" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18">
       <c r="A19" s="33"/>
       <c r="B19" s="31" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="22" customFormat="1" ht="18">
       <c r="A20" s="30"/>
       <c r="B20" s="31" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18">
       <c r="A21" s="33"/>
       <c r="B21" s="31" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18">
       <c r="A22" s="33"/>
       <c r="B22" s="35" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18">
@@ -15344,14 +15377,14 @@
     </row>
     <row r="24" spans="1:3" ht="18">
       <c r="A24" s="124" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B24" s="124"/>
     </row>
     <row r="25" spans="1:3" ht="43.5">
       <c r="A25" s="33"/>
       <c r="B25" s="31" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18">
@@ -15361,19 +15394,19 @@
     <row r="27" spans="1:3" ht="18">
       <c r="A27" s="33"/>
       <c r="B27" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18">
       <c r="A28" s="33"/>
       <c r="B28" s="31" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="28.5">
       <c r="A29" s="33"/>
       <c r="B29" s="31" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18">
@@ -15383,19 +15416,19 @@
     <row r="31" spans="1:3" ht="18">
       <c r="A31" s="33"/>
       <c r="B31" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18">
       <c r="A32" s="33"/>
       <c r="B32" s="31" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="18">
       <c r="A33" s="33"/>
       <c r="B33" s="31" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18">
@@ -15405,13 +15438,13 @@
     <row r="35" spans="1:2" ht="28.5">
       <c r="A35" s="33"/>
       <c r="B35" s="31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="18">
       <c r="A36" s="33"/>
       <c r="B36" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="18">
@@ -15420,28 +15453,28 @@
     </row>
     <row r="38" spans="1:2" ht="18">
       <c r="A38" s="124" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B38" s="124"/>
     </row>
     <row r="39" spans="1:2" ht="28.5">
       <c r="B39" s="31" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.25">
       <c r="B41" s="31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="28.5">
       <c r="B43" s="31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="28.5">
       <c r="B45" s="31" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -15449,102 +15482,102 @@
     </row>
     <row r="47" spans="1:2" ht="28.5">
       <c r="B47" s="31" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="18">
       <c r="A49" s="124" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B49" s="124"/>
     </row>
     <row r="50" spans="1:2" ht="28.5">
       <c r="B50" s="31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25">
       <c r="A52" s="40" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B52" s="31" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25">
       <c r="A53" s="40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.25">
       <c r="A54" s="40" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B54" s="31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="28.5">
       <c r="A55" s="29"/>
       <c r="B55" s="31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="28.5">
       <c r="A56" s="29"/>
       <c r="B56" s="31" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.25">
       <c r="A57" s="40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.25">
       <c r="A58" s="29"/>
       <c r="B58" s="31" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.25">
       <c r="A59" s="29"/>
       <c r="B59" s="31" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.25">
       <c r="A60" s="40" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="28.5">
       <c r="A61" s="29"/>
       <c r="B61" s="31" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.25">
       <c r="A62" s="40" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.25">
       <c r="A63" s="41"/>
       <c r="B63" s="31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -15552,33 +15585,33 @@
     </row>
     <row r="65" spans="1:2" ht="18">
       <c r="A65" s="124" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B65" s="124"/>
     </row>
     <row r="66" spans="1:2" ht="42.75">
       <c r="B66" s="31" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="18">
       <c r="A68" s="124" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B68" s="124"/>
     </row>
     <row r="69" spans="1:2" ht="15">
       <c r="A69" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B69" s="44" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="28.5">
       <c r="A70" s="41"/>
       <c r="B70" s="45" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.25">
@@ -15587,16 +15620,16 @@
     </row>
     <row r="72" spans="1:2" ht="15">
       <c r="A72" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B72" s="44" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="28.5">
       <c r="A73" s="41"/>
       <c r="B73" s="45" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.25">
@@ -15605,16 +15638,16 @@
     </row>
     <row r="75" spans="1:2" ht="15">
       <c r="A75" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B75" s="47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="42.75">
       <c r="A76" s="41"/>
       <c r="B76" s="28" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.25">
@@ -15623,16 +15656,16 @@
     </row>
     <row r="78" spans="1:2" ht="15">
       <c r="A78" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B78" s="47" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="28.5">
       <c r="A79" s="41"/>
       <c r="B79" s="28" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.25">
@@ -15641,28 +15674,28 @@
     </row>
     <row r="81" spans="1:2" ht="15">
       <c r="A81" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B81" s="47" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="14.25">
       <c r="A82" s="41"/>
       <c r="B82" s="48" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="14.25">
       <c r="A83" s="41"/>
       <c r="B83" s="48" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="14.25">
       <c r="A84" s="41"/>
       <c r="B84" s="48" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="15">
@@ -15671,28 +15704,28 @@
     </row>
     <row r="86" spans="1:2" ht="15">
       <c r="A86" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B86" s="47" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="42.75">
       <c r="A87" s="41"/>
       <c r="B87" s="28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="14.25">
       <c r="A88" s="41"/>
       <c r="B88" s="109" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="57">
       <c r="A89" s="41"/>
       <c r="B89" s="110" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="14.25">
@@ -15701,21 +15734,21 @@
     </row>
     <row r="91" spans="1:2" ht="15">
       <c r="A91" s="43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B91" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="28.5">
       <c r="A92" s="29"/>
       <c r="B92" s="48" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -15752,7 +15785,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B1" s="12"/>
     </row>
@@ -15762,14 +15795,14 @@
     <row r="3" spans="1:3" ht="15">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C3" s="14"/>
     </row>
     <row r="4" spans="1:3" ht="14.25">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="16"/>
     </row>
@@ -15781,7 +15814,7 @@
     <row r="6" spans="1:3" ht="15.75">
       <c r="A6" s="16"/>
       <c r="B6" s="19" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C6" s="16"/>
     </row>
@@ -15793,7 +15826,7 @@
     <row r="8" spans="1:3" ht="30">
       <c r="A8" s="16"/>
       <c r="B8" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C8" s="16"/>
     </row>
@@ -15805,7 +15838,7 @@
     <row r="10" spans="1:3" ht="46.5">
       <c r="A10" s="16"/>
       <c r="B10" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C10" s="16"/>
     </row>
@@ -15817,7 +15850,7 @@
     <row r="12" spans="1:3" ht="45">
       <c r="A12" s="16"/>
       <c r="B12" s="18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C12" s="16"/>
     </row>
@@ -15829,7 +15862,7 @@
     <row r="14" spans="1:3" ht="60">
       <c r="A14" s="16"/>
       <c r="B14" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C14" s="16"/>
     </row>
@@ -15841,7 +15874,7 @@
     <row r="16" spans="1:3" ht="30.75">
       <c r="A16" s="16"/>
       <c r="B16" s="18" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C16" s="16"/>
     </row>
@@ -15853,14 +15886,14 @@
     <row r="18" spans="1:3" ht="15.75">
       <c r="A18" s="16"/>
       <c r="B18" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C18" s="16"/>
     </row>
     <row r="19" spans="1:3" ht="15">
       <c r="A19" s="16"/>
       <c r="B19" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C19" s="16"/>
     </row>
@@ -15927,15 +15960,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="49.7109375" customWidth="1"/>
+    <col min="1" max="1" width="70.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="37.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -15950,14 +15983,19 @@
       <c r="L1" s="125"/>
       <c r="M1" s="125"/>
     </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>236</v>
+      </c>
+    </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15975,34 +16013,14 @@
         <v>241</v>
       </c>
     </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="134" t="s">
+        <v>245</v>
+      </c>
+    </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
+      <c r="A10" s="134" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -16034,30 +16052,30 @@
     </row>
     <row r="3" spans="1:66" ht="15">
       <c r="A3" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:66" ht="15">
       <c r="A4" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:66" ht="15">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:66">
       <c r="A6" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:66">
       <c r="A7" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:66" s="1" customFormat="1" ht="18">
@@ -16066,7 +16084,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -16154,7 +16172,7 @@
         <v>0.2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>19</v>
@@ -16242,7 +16260,7 @@
         <v>0.3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -16330,7 +16348,7 @@
         <v>0.4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>19</v>
@@ -16418,7 +16436,7 @@
         <v>0.5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -16502,7 +16520,7 @@
     </row>
     <row r="22" spans="1:66">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
